--- a/excel/output_stats_vfvv/ludcmp/PerSubgraphStats.xlsx
+++ b/excel/output_stats_vfvv/ludcmp/PerSubgraphStats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
         <v>63</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
         <v>46</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
         <v>51</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>13</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
         <v>38</v>
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>14899200000</v>
+        <v>14901100000</v>
       </c>
       <c r="K16" t="n">
         <v>59569100000</v>
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2514230</v>
+        <v>4004270</v>
       </c>
       <c r="K18" t="n">
         <v>17476700</v>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>8004</v>
+        <v>9004.5</v>
       </c>
       <c r="K20" t="n">
         <v>40020</v>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K21" t="n">
         <v>53</v>
@@ -1469,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
         <v>30</v>
@@ -1481,10 +1481,10 @@
         <v>0.6</v>
       </c>
       <c r="N22" t="n">
-        <v>352.457</v>
+        <v>340.319</v>
       </c>
       <c r="O22" t="n">
-        <v>355.12</v>
+        <v>342.99</v>
       </c>
     </row>
     <row r="23">
@@ -1528,10 +1528,10 @@
         <v>0.6</v>
       </c>
       <c r="N23" t="n">
-        <v>352.457</v>
+        <v>340.319</v>
       </c>
       <c r="O23" t="n">
-        <v>355.16</v>
+        <v>343.06</v>
       </c>
     </row>
     <row r="24">
@@ -1575,10 +1575,10 @@
         <v>0.6</v>
       </c>
       <c r="N24" t="n">
-        <v>351.298</v>
+        <v>339.162</v>
       </c>
       <c r="O24" t="n">
-        <v>353.96</v>
+        <v>341.87</v>
       </c>
     </row>
     <row r="25">
@@ -1622,10 +1622,10 @@
         <v>0.6</v>
       </c>
       <c r="N25" t="n">
-        <v>351.297</v>
+        <v>339.161</v>
       </c>
       <c r="O25" t="n">
-        <v>353.95</v>
+        <v>343.82</v>
       </c>
     </row>
     <row r="26">
@@ -1669,10 +1669,10 @@
         <v>0.6</v>
       </c>
       <c r="N26" t="n">
-        <v>350.151</v>
+        <v>337.978</v>
       </c>
       <c r="O26" t="n">
-        <v>350.23</v>
+        <v>346.45</v>
       </c>
     </row>
     <row r="27">
@@ -1680,34 +1680,34 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>1.67388e-09</v>
+        <v>4.33547</v>
       </c>
       <c r="D27" t="n">
-        <v>5.83333e-09</v>
+        <v>8.10427</v>
       </c>
       <c r="E27" t="n">
-        <v>0.286951</v>
+        <v>0.534962</v>
       </c>
       <c r="F27" t="n">
-        <v>9.764290000000002e-18</v>
+        <v>35.1358</v>
       </c>
       <c r="G27" t="n">
-        <v>857143000</v>
+        <v>819895000</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>6644650000</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>5975670000</v>
       </c>
       <c r="K27" t="n">
-        <v>21</v>
+        <v>29175400000</v>
       </c>
       <c r="L27" t="n">
         <v>3600000000</v>
@@ -1716,10 +1716,10 @@
         <v>0.6</v>
       </c>
       <c r="N27" t="n">
-        <v>350.151</v>
+        <v>337.977</v>
       </c>
       <c r="O27" t="n">
-        <v>350.2</v>
+        <v>358.28</v>
       </c>
     </row>
     <row r="28">
@@ -1727,25 +1727,25 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>5.73265e-09</v>
+        <v>1.67388e-09</v>
       </c>
       <c r="D28" t="n">
-        <v>1.97222e-08</v>
+        <v>5.83333e-09</v>
       </c>
       <c r="E28" t="n">
-        <v>0.29067</v>
+        <v>0.286951</v>
       </c>
       <c r="F28" t="n">
-        <v>1.13061e-16</v>
+        <v>9.764290000000002e-18</v>
       </c>
       <c r="G28" t="n">
-        <v>963380000</v>
+        <v>857143000</v>
       </c>
       <c r="H28" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1754,7 +1754,7 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="L28" t="n">
         <v>3600000000</v>
@@ -1763,10 +1763,10 @@
         <v>0.6</v>
       </c>
       <c r="N28" t="n">
-        <v>350.15</v>
+        <v>350.151</v>
       </c>
       <c r="O28" t="n">
-        <v>350.18</v>
+        <v>350.2</v>
       </c>
     </row>
     <row r="29">
@@ -1774,34 +1774,34 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" t="n">
-        <v>4.64603e-10</v>
+        <v>5.73265e-09</v>
       </c>
       <c r="D29" t="n">
-        <v>1.66667e-09</v>
+        <v>1.97222e-08</v>
       </c>
       <c r="E29" t="n">
-        <v>0.278762</v>
+        <v>0.29067</v>
       </c>
       <c r="F29" t="n">
-        <v>7.74338e-19</v>
+        <v>1.13061e-16</v>
       </c>
       <c r="G29" t="n">
-        <v>600000000</v>
+        <v>963380000</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="L29" t="n">
         <v>3600000000</v>
@@ -1813,7 +1813,7 @@
         <v>350.15</v>
       </c>
       <c r="O29" t="n">
-        <v>350.17</v>
+        <v>350.18</v>
       </c>
     </row>
     <row r="30">
@@ -1821,7 +1821,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" t="n">
         <v>4.64603e-10</v>
@@ -1868,34 +1868,34 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" t="n">
-        <v>6.10341e-10</v>
+        <v>4.64603e-10</v>
       </c>
       <c r="D31" t="n">
-        <v>1.94444e-09</v>
+        <v>1.66667e-09</v>
       </c>
       <c r="E31" t="n">
-        <v>0.31389</v>
+        <v>0.278762</v>
       </c>
       <c r="F31" t="n">
-        <v>1.18677e-18</v>
+        <v>7.74338e-19</v>
       </c>
       <c r="G31" t="n">
-        <v>1028570000</v>
+        <v>600000000</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
         <v>3600000000</v>
@@ -1904,10 +1904,10 @@
         <v>0.6</v>
       </c>
       <c r="N31" t="n">
-        <v>350.151</v>
+        <v>350.15</v>
       </c>
       <c r="O31" t="n">
-        <v>350.18</v>
+        <v>350.17</v>
       </c>
     </row>
     <row r="32">
@@ -1915,7 +1915,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32" t="n">
         <v>6.10341e-10</v>
@@ -1962,34 +1962,34 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" t="n">
-        <v>1.45203e-09</v>
+        <v>6.10341e-10</v>
       </c>
       <c r="D33" t="n">
-        <v>4.72222e-09</v>
+        <v>1.94444e-09</v>
       </c>
       <c r="E33" t="n">
-        <v>0.30749</v>
+        <v>0.31389</v>
       </c>
       <c r="F33" t="n">
-        <v>6.85683e-18</v>
+        <v>1.18677e-18</v>
       </c>
       <c r="G33" t="n">
-        <v>847059000</v>
+        <v>1028570000</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L33" t="n">
         <v>3600000000</v>
@@ -2009,34 +2009,34 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" t="n">
-        <v>1.19266e-10</v>
+        <v>1.45203e-09</v>
       </c>
       <c r="D34" t="n">
-        <v>2.77778e-10</v>
+        <v>4.72222e-09</v>
       </c>
       <c r="E34" t="n">
-        <v>0.429359</v>
+        <v>0.30749</v>
       </c>
       <c r="F34" t="n">
-        <v>3.31295e-20</v>
+        <v>6.85683e-18</v>
       </c>
       <c r="G34" t="n">
-        <v>3600000000</v>
+        <v>847059000</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L34" t="n">
         <v>3600000000</v>
@@ -2048,6 +2048,53 @@
         <v>350.151</v>
       </c>
       <c r="O34" t="n">
+        <v>350.18</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.19266e-10</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2.77778e-10</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.429359</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.31295e-20</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3600000000</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N35" t="n">
+        <v>350.151</v>
+      </c>
+      <c r="O35" t="n">
         <v>350.23</v>
       </c>
     </row>
